--- a/data/trans_orig/IP16CS1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Estudios-trans_orig.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>501</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>369</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16CS1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,74 +1402,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5310</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6967</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2495</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>48,18%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6408</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3733</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8082</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,04%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>41,97%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>695</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -1741,82 +1741,82 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3069</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1854,82 +1854,82 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4367</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7597</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7597</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7597</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,67 +2084,67 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4989</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2874</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>766</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>766</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3717</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -2536,82 +2536,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1594</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>5716</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>5716</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>5716</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8670</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>8048</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10108</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3756</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4932</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -3105,82 +3105,82 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2576</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4950</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>311</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
